--- a/artfynd/A 60564-2025 artfynd.xlsx
+++ b/artfynd/A 60564-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121184609</v>
+        <v>121184580</v>
       </c>
       <c r="B2" t="n">
-        <v>58184</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,10 +704,13 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -764,7 +762,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,19 +789,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121184580</v>
+        <v>121202036</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -828,11 +820,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>793354</v>
+        <v>793368</v>
       </c>
       <c r="R3" t="n">
-        <v>7192973</v>
+        <v>7192987</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -911,32 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121202036</v>
+        <v>121202010</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>793368</v>
+        <v>793405</v>
       </c>
       <c r="R4" t="n">
-        <v>7192987</v>
+        <v>7193058</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1015,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Högdahl, Amanda Johansson</t>
+          <t>Amanda Johansson, Anna Högdahl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1026,32 +1009,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121202010</v>
+        <v>121184609</v>
       </c>
       <c r="B5" t="n">
-        <v>56560</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1060,6 +1038,7 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -1070,13 +1049,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>793405</v>
+        <v>793354</v>
       </c>
       <c r="R5" t="n">
-        <v>7193058</v>
+        <v>7192973</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,6 +1093,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,6 +1114,117 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering AFRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121184670</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99026</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219788</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bergsbyn, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>793440</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7192937</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Intermediärt kärr</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna Högdahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Högdahl, Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Naturvärdesinventering AFRY</t>
         </is>

--- a/artfynd/A 60564-2025 artfynd.xlsx
+++ b/artfynd/A 60564-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Naturvärdesinventering AFRY</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121184580</t>
         </is>
       </c>
     </row>
@@ -896,6 +906,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121202036</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Naturvärdesinventering AFRY</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121202010</t>
         </is>
       </c>
     </row>
@@ -1118,6 +1138,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121184609</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,8 +1254,20 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121184670</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>